--- a/docs/m365/Global_AR_回收統計範本.xlsx
+++ b/docs/m365/Global_AR_回收統計範本.xlsx
@@ -12958,7 +12958,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>選項文字須與 Forms 的 R0 選項完全一致;一般不需修改</t>
+          <t>選項文字須與表單的 R0 選項完全一致;一般不需修改</t>
         </is>
       </c>
     </row>
